--- a/Agenda de Entregas Renato Oliveira Móveis Planejados.xlsx
+++ b/Agenda de Entregas Renato Oliveira Móveis Planejados.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>Cliente</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Parcelou em quantas vezes</t>
+  </si>
+  <si>
+    <t>Lucas</t>
   </si>
 </sst>
 </file>
@@ -404,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -465,14 +468,14 @@
         <v>7</v>
       </c>
       <c r="E2" s="2">
-        <v>15200</v>
+        <v>15600</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
       </c>
       <c r="G2" s="2">
         <f>C2-E2</f>
-        <v>16000</v>
+        <v>15600</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>7</v>
@@ -548,6 +551,38 @@
       </c>
       <c r="J4" s="3">
         <v>46224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>17000</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2">
+        <v>17000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>46214</v>
       </c>
     </row>
   </sheetData>
